--- a/aq_files/0372.xlsx
+++ b/aq_files/0372.xlsx
@@ -1,165 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>Job_ID,Job_Name,Combiner_Enabled,Combiner_Input_Records,Combiner_Output_Records,Combiner_Reduction_Ratio,Spill_Count,Spill_To_Disk_MB,Shuffle_Input_MB,Shuffle_Output_MB,Shuffle_Time_Sec,Shuffle_Transfer_Rate_MBps,Sort_Time_Sec,Sort_Method,Sort_Records,Group_Time_Sec,Group_Count,Intermediate_Compression,Compression_Codec,Network_Copied_MB,Local_Copied_MB,Reduce_Input_MB,Reduce_Output_MB,Total_Shuffle_Connections,Shuffle_Error_Count,Sort_Spill_Count,Success_Status</t>
-  </si>
-  <si>
-    <t>JOB-001,WordCount,Yes,2500000,450000,5.56,12,256,3200,2800,12,267,8,QuickSort,2500000,15,1800000,Yes,Snappy,2400,800,2800,256,64,0,2,Success</t>
-  </si>
-  <si>
-    <t>JOB-002,LogParser,Yes,9800000,1890000,5.19,28,512,6500,5600,24,271,12,QuickSort,9800000,18,6400000,Yes,Snappy,4800,1700,5600,512,128,0,3,Success</t>
-  </si>
-  <si>
-    <t>JOB-003,SalesAgg,Yes,1250000,210000,5.95,8,128,1800,1600,8,225,5,QuickSort,1250000,10,320000,Yes,Snappy,1200,600,1600,32,32,0,1,Success</t>
-  </si>
-  <si>
-    <t>JOB-004,ClickStream,Yes,31500000,8250000,3.82,56,1024,19200,16800,36,533,22,ExternalSort,31500000,28,16800000,Yes,Snappy,14400,4800,16800,19200,384,2,6,Partial</t>
-  </si>
-  <si>
-    <t>JOB-005,UserSegment,Yes,1890000,315000,6.00,34,768,9600,8400,36,267,14,QuickSort,1890000,19,960000,Yes,Snappy,7200,2400,8400,9600,192,0,4,Success</t>
-  </si>
-  <si>
-    <t>JOB-006,FraudDetect,Yes,21500000,890000,24.16,78,2048,25600,12800,96,267,18,ExternalSort,21500000,25,1600000,Yes,Zlib,9600,3200,12800,1600,512,3,8,Partial</t>
-  </si>
-  <si>
-    <t>JOB-007,PageRank,Yes,12000000,12000000,1.00,18,256,12800,12800,24,533,45,QuickSort,12000000,56,12000000,Yes,Snappy,9600,3200,12800,12800,128,0,2,Success</t>
-  </si>
-  <si>
-    <t>JOB-008,ImageProcess,Yes,2500000,1250000,2.00,95,2048,51200,51200,72,711,56,ExternalSort,2500000,72,1250000,No,None,38400,12800,51200,51200,1024,5,12,Partial</t>
-  </si>
-  <si>
-    <t>JOB-009,ETL_Cleansing,Yes,32500000,6500000,5.00,112,4096,76800,76800,108,711,45,ExternalSort,32500000,68,15360000,Yes,Snappy,57600,19200,76800,76800,768,1,8,Success</t>
-  </si>
-  <si>
-    <t>JOB-010,SearchIndex,Yes,25000000,25000000,1.00,24,512,25600,25600,36,711,56,QuickSort,25000000,89,50000000,Yes,Gzip,19200,6400,25600,25600,256,0,3,Success</t>
-  </si>
-  <si>
-    <t>JOB-011,SensorData,Yes,5200000,1250000,4.16,14,256,2100,1800,8,263,6,QuickSort,5200000,12,3200000,Yes,Snappy,1400,700,1800,3200,64,0,2,Success</t>
-  </si>
-  <si>
-    <t>JOB-012,SocialNet,Yes,21700000,10800000,2.01,56,1024,25600,25600,36,711,42,ExternalSort,21700000,58,10800000,Yes,Snappy,19200,6400,25600,25600,256,1,5,Success</t>
-  </si>
-  <si>
-    <t>JOB-013,Recommend,Yes,5400000,1800000,3.00,32,512,19200,19200,24,800,28,QuickSort,5400000,35,2560000,Yes,Snappy,14400,4800,19200,19200,128,0,3,Success</t>
-  </si>
-  <si>
-    <t>JOB-014,GenomeSeq,Yes,35000000,12500000,2.80,145,8192,89600,89600,156,574,78,ExternalSort,35000000,95,10240000,Yes,Zlib,67200,22400,89600,102400,2048,4,15,Partial</t>
-  </si>
-  <si>
-    <t>JOB-015,LogAnalytics,Yes,25800000,6300000,4.10,68,1536,38400,38400,48,800,38,ExternalSort,25800000,52,12600000,Yes,Snappy,28800,9600,38400,38400,384,1,5,Success</t>
-  </si>
-  <si>
-    <t>JOB-016,UserProfile,Yes,9600000,2400000,4.00,28,512,4800,4800,16,300,12,QuickSort,9600000,18,9600000,Yes,Snappy,3600,1200,4800,9600,96,0,2,Success</t>
-  </si>
-  <si>
-    <t>JOB-017,ClickPrediction,Yes,12800000,6400000,2.00,42,768,9600,9600,24,400,16,QuickSort,12800000,22,12800000,Yes,Snappy,7200,2400,9600,12800,128,0,3,Success</t>
-  </si>
-  <si>
-    <t>JOB-018,DataValidation,Yes,6400000,1600000,4.00,18,256,3200,3200,10,320,8,QuickSort,6400000,12,6400000,Yes,Snappy,2400,800,3200,6400,64,0,1,Success</t>
-  </si>
-  <si>
-    <t>JOB-019,BackupOperation,Yes,87200000,43600000,2.00,112,4096,102400,102400,144,711,56,ExternalSort,87200000,72,20480000,Yes,Zlib,76800,25600,102400,204800,1024,3,9,Partial</t>
-  </si>
-  <si>
-    <t>JOB-020,RealTimeAnalytics,Yes,19200000,9600000,2.00,56,1024,19200,19200,32,600,24,QuickSort,19200000,28,19200000,Yes,Snappy,14400,4800,19200,19200,128,0,4,Success</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Key_Concept,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is a Combiner in MapReduce? Explain its purpose and benefits using the dataset.","Combiner Overview","Analyze Combiner_Enabled, Combiner_Reduction_Ratio","Combiner performs local aggregation. Reduction ratio: 1.0-24.2x. Avg reduction: 4.8x. FraudDetect highest reduction (24x)","Combiner reduces data transferred during shuffle by performing local aggregation"</t>
-  </si>
-  <si>
-    <t>2,"What is Combiner reduction ratio? Calculate average reduction and identify best/worst cases.","Combiner Efficiency","Analyze Combiner_Reduction_Ratio","Average reduction: 4.8x (80% reduction). Best: FraudDetect (24.2x), SalesAgg (5.95x); Worst: PageRank (1.0x), SearchIndex (1.0x)","Higher reduction means more efficient combiner; ratio depends on job type"</t>
-  </si>
-  <si>
-    <t>3,"When does a Combiner not help? Analyze jobs with low combiner reduction ratio.","Combiner Limitations","Filter Combiner_Reduction_Ratio &lt; 2.0","Jobs: PageRank (1.0), SearchIndex (1.0), SocialNet (2.01), GenomeSeq (2.8). No reduction when keys are mostly unique","Combiner ineffective when keys are unique; no local aggregation possible"</t>
-  </si>
-  <si>
-    <t>4,"What is the relationship between combiner reduction and spill count? Analyze correlation.","Combiner vs Spill","Correlate Combiner_Reduction_Ratio vs Spill_Count","High reduction (24x) reduces spills (78); Low reduction (1x) also has low spills (18-24). Moderate reduction (3-6x) has highest spills (56-145)","More spills occur when combiner reduces but memory still insufficient"</t>
-  </si>
-  <si>
-    <t>5,"What is Spill in MapReduce? Explain spill count and its impact on performance.","Spill Overview","Analyze Spill_Count, Spill_To_Disk_MB","Spill count: 8-145 per job; Spill to disk: 128-8,192 MB. GenomeSeq: 145 spills (8GB), ImageProcess: 95 spills (2GB)","Spills occur when map output exceeds memory buffer; impacts performance"</t>
-  </si>
-  <si>
-    <t>6,"What is the Shuffle phase? Explain its purpose and components from the dataset.","Shuffle Overview","Analyze Shuffle_Input_MB, Shuffle_Time_Sec","Shuffle transfers data from mappers to reducers. Data: 1,800-102,400 MB; Time: 8-156 sec; Transfer rate: 225-800 MBps","Shuffle is the most network-intensive phase; optimization critical"</t>
-  </si>
-  <si>
-    <t>7,"What is shuffle transfer rate? Calculate average and analyze factors affecting it.","Shuffle Performance","Calculate Shuffle_Transfer_Rate_MBps","Average rate: 484 MBps. Highest: ImageProcess (711 MBps), SearchIndex (711 MBps); Lowest: SalesAgg (225 MBps)","Transfer rate affected by network, compression, and data distribution"</t>
-  </si>
-  <si>
-    <t>8,"What is the difference between network copied and local copied data? Analyze from dataset.","Shuffle Data Sources","Compare Network_Copied_MB vs Local_Copied_MB","Network copied: 1,200-76,800 MB (75% of shuffle); Local copied: 600-25,600 MB (25%). Local copies avoid network","Local copies from same node reduce network traffic significantly"</t>
-  </si>
-  <si>
-    <t>9,"What is Intermediate Compression? Analyze its usage and impact on shuffle.","Compression in Shuffle","Analyze Intermediate_Compression, Compression_Codec","Intermediate compression enabled: 90% (18/20). Codecs: Snappy (70%), Zlib (15%), Gzip (5%), None (10%)","Compression reduces shuffle data by 2-6x; Snappy is most common"</t>
-  </si>
-  <si>
-    <t>10,"What is Sort in MapReduce? Explain the sorting phase and methods used.","Sort Overview","Analyze Sort_Time_Sec, Sort_Method, Sort_Records","Sort time: 5-78 sec. Methods: QuickSort (60%), ExternalSort (40%). Sort records: 1.25M-87M records","Sorting groups keys together before reduce phase"</t>
-  </si>
-  <si>
-    <t>11,"What is the difference between QuickSort and ExternalSort? When is each used?","Sort Methods","Compare Sort_Method across jobs","QuickSort: Used for smaller data (&lt;25M records), faster; ExternalSort: Used for larger data, handles spills. GenomeSeq uses ExternalSort for 87M records","ExternalSort handles data exceeding memory; QuickSort for in-memory"</t>
-  </si>
-  <si>
-    <t>12,"What is Grouping in MapReduce? Explain group time and its relationship to unique keys.","Grouping Overview","Analyze Group_Time_Sec, Group_Count","Group time: 10-95 sec. Groups all values for each key. Group_Count = number of unique keys (320K-50M)","Grouping assembles all values for each key for reduce function"</t>
-  </si>
-  <si>
-    <t>13,"What is the relationship between sort time and group time? Analyze from dataset.","Sort vs Group","Compare Sort_Time_Sec vs Group_Time_Sec","Sort time: 5-78 sec; Group time: 10-95 sec. Group time is 1.5-2x sort time. Both scale with data volume","Sort prepares keys; grouping organizes values; both essential"</t>
-  </si>
-  <si>
-    <t>14,"What is reduce input vs reduce output? Analyze data reduction during reduce phase.","Reduce Data Flow","Compare Reduce_Input_MB vs Reduce_Output_MB","Reduce input: 1,600-102,400 MB; Reduce output: 32-204,800 MB. Overall reduction: 32-80% depending on job","Reduce phase further reduces or expands data based on aggregation"</t>
-  </si>
-  <si>
-    <t>15,"What are shuffle errors? Identify jobs with shuffle errors and analyze patterns.","Shuffle Reliability","Filter Shuffle_Error_Count &gt; 0","Shuffle errors: ClickStream (2), FraudDetect (3), ImageProcess (5), GenomeSeq (4), BackupOperation (3). Errors increase with shuffle size","Larger shuffle data increases chance of network errors; retry mechanism handles"</t>
-  </si>
-  <si>
-    <t>16,"What is sort spill count? Analyze its relationship with overall spills.","Sort Spills","Analyze Sort_Spill_Count","Sort spills: 1-15 per job. Correlates with Spill_Count (r=0.85). Larger jobs have more sort spills","Sort spills occur when data doesn't fit in memory during sorting"</t>
-  </si>
-  <si>
-    <t>17,"What is the complete data flow from mapper to reducer? Trace data through phases.","End-to-End Flow","Trace data: Map → Combiner → Spill → Shuffle → Sort → Group → Reduce","Map output (100%) → Combiner (20-80% reduction) → Spill to disk → Shuffle (network) → Sort → Group → Reduce output","Each phase transforms data; combiner and compression optimize shuffle"</t>
-  </si>
-  <si>
-    <t>18,"What are the performance bottlenecks in shuffle and sort? Identify from dataset.","Bottleneck Analysis","Analyze longest phases","Shuffle bottleneck: GenomeSeq (156 sec, 89.6GB); Sort bottleneck: GenomeSeq (78 sec, 87M records); Group: GenomeSeq (95 sec)","Large data volumes cause bottlenecks; tuning needed for large jobs"</t>
-  </si>
-  <si>
-    <t>19,"How does combiner efficiency affect shuffle size? Analyze correlation.","Combiner-Shuffle Correlation","Correlate Combiner_Reduction_Ratio vs Shuffle_Input_MB","High combiner reduction (24x) reduces shuffle to 12.8GB (FraudDetect); Low combiner (1x) keeps shuffle at 25.6GB (SearchIndex)","Effective combiner reduces shuffle data 2-24x, improving performance"</t>
-  </si>
-  <si>
-    <t>20,"Create a MapReduce optimization checklist based on combiner, shuffle, and sort metrics.","Optimization Guide","Summarize best practices from metrics","1. Enable combiner (4.8x avg reduction) 2. Use compression (90% jobs) 3. Monitor spills (&gt;100 indicates memory issues) 4. Optimize sort method 5. Balance partitions","Combiner, compression, and memory tuning optimize MapReduce jobs"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -169,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -393,235 +316,963 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_ID,Order_Date,Product_Name,Category,Sales_Amount,Quantity,Discount,Profit,Region,Status,Return_Flag,Customer_Notes,Import_Date</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,2024-01-05,MacBook Pro,Electronics,1299.99,1,0.05,389.99,North,Active,N,"Premium customer",2024-01-05</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,2024-01-05,Magic Mouse,Electronics,79.99,3,0.10,23.99,North,Active,N,"",2024-01-05</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,2024-01-06,Designer Jeans,Clothing,89.99,2,0.00,26.99,South,Active,N,"First time customer",2024-01-06</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,2024-01-06,27-inch Monitor,Electronics,299.99,1,0.15,89.99,South,Active,N,"",2024-01-06</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,2024-01-07,Executive Chair,Furniture,399.99,2,0.05,119.99,East,Active,N,"VIP customer",2024-01-07</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,2024-01-07,Mechanical Keyboard,Electronics,89.99,2,0.10,26.99,East,Delayed,N,"",2024-01-07</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,2024-01-08,Leather Jacket,Clothing,199.99,1,0.20,59.99,West,Active,N,"",2024-01-08</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,2024-01-08,iPad,Electronics,499.99,1,0.05,149.99,West,Active,N,"",2024-01-08</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,2024-01-09,Floor Lamp,Furniture,79.99,2,0.00,23.99,North,Active,N,"",2024-01-09</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,2024-01-09,Running Shoes,Clothing,69.99,1,0.10,20.99,North,Returned,Y,"Size issue",2024-01-09</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,2024-01-10,Gaming Laptop,Electronics,1299.99,1,0.15,389.99,South,Active,N,"",2024-01-10</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,2024-01-10,Headphones,Electronics,149.99,2,0.05,44.99,East,Active,N,"",2024-01-10</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,2024-01-11,Wool Coat,Clothing,189.99,1,0.20,56.99,West,Active,N,"",2024-01-11</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,2024-01-11,Bookshelf,Furniture,159.99,1,0.10,47.99,North,Active,N,"",2024-01-11</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,2024-01-12,Smartphone,Electronics,699.99,2,0.05,209.99,South,Active,N,"",2024-01-12</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,2024-01-12,Dress Shirt,Clothing,59.99,3,0.00,17.99,East,Active,N,"",2024-01-12</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,2024-01-13,External SSD,Electronics,99.99,1,0.10,29.99,West,Active,N,"",2024-01-13</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,2024-01-13,Hoodie,Clothing,49.99,2,0.05,14.99,North,Returned,Y,"Wrong size",2024-01-13</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,2024-01-14,Gaming Desk,Furniture,349.99,1,0.15,104.99,South,Active,N,"",2024-01-14</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,2024-01-14,Webcam,Electronics,79.99,2,0.10,23.99,East,Active,N,"",2024-01-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,2024-02-01,Docking Station,Electronics,129.99,1,0.00,38.99,West,Active,N,"",2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,2024-02-01,Winter Parka,Clothing,179.99,1,0.05,53.99,North,Active,N,"",2024-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,2024-02-02,Office Desk,Furniture,449.99,1,0.10,134.99,South,Active,N,"",2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,2024-02-02,USB-C Hub,Electronics,39.99,3,0.00,11.99,East,Active,N,"",2024-02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,2024-02-03,Casual Blazer,Clothing,149.99,1,0.15,44.99,West,Active,N,"",2024-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,Gaming Mouse,Electronics,59.99,2,0.10,17.99,North,Returned,Y,"Defective product",2024-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,Laser Printer,Electronics,199.99,1,0.05,59.99,South,Active,N,"",2024-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,Lounge Chair,Furniture,279.99,1,0.20,83.99,East,Active,N,"",2024-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,Power Bank,Electronics,49.99,4,0.00,14.99,West,Active,N,"",2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,Wool Scarf,Clothing,24.99,5,0.10,7.49,North,Active,N,"",2024-02-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,Gaming Headset,Electronics,119.99,1,0.05,35.99,South,Active,N,"",2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,Night Stand,Furniture,69.99,2,0.10,20.99,East,Active,N,"",2024-02-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,Athletic Shoes,Clothing,109.99,1,0.15,32.99,West,Active,N,"",2024-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,Smart Watch,Electronics,199.99,1,0.05,59.99,North,Active,N,"",2024-02-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,Bluetooth Speaker,Electronics,79.99,2,0.10,23.99,South,Active,N,"",2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,Cashmere Sweater,Clothing,99.99,1,0.00,29.99,East,Returned,Y,"Quality issue",2024-02-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,Bookshelf,Furniture,129.99,1,0.05,38.99,West,Active,N,"",2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,Mesh Router,Electronics,99.99,1,0.10,29.99,North,Active,N,"",2024-02-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,Golf Polo,Clothing,44.99,3,0.15,13.49,South,Active,N,"",2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,Graphics Card,Electronics,499.99,1,0.20,149.99,West,Active,N,"",2024-02-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,Desktop PC,Electronics,999.99,1,0.05,299.99,North,Active,N,"",2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,Yoga Pants,Clothing,49.99,2,0.00,14.99,South,Active,N,"",2024-03-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,Coffee Table,Furniture,249.99,1,0.10,74.99,East,Active,N,"",2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,Smart Speaker,Electronics,89.99,2,0.00,26.99,West,Active,N,"",2024-03-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,Baseball Cap,Clothing,19.99,4,0.05,5.99,North,Active,N,"",2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,Quadcopter,Electronics,349.99,1,0.10,104.99,South,Active,N,"",2024-03-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,Wall Mirror,Furniture,59.99,2,0.00,17.99,East,Active,N,"",2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,Flannel Shirt,Clothing,49.99,2,0.10,14.99,West,Active,N,"",2024-03-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,Streaming Stick,Electronics,29.99,3,0.05,8.99,North,Returned,Y,"Not working properly",2024-03-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,Leggings,Clothing,29.99,4,0.00,8.99,South,Active,N,"",2024-03-05</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Load the dataset into Power Query Editor. Remove the top 2 rows from the dataset. How many rows remain after removal?</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Remove the bottom 5 rows from the dataset. How many rows remain after removal?</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>24</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Remove all duplicate rows based on 'Order_ID' column. How many duplicates were found? How many rows remain?</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Remove rows where 'Status' column contains 'Returned'. How many rows are removed? How many active orders remain?</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>26</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to keep only 'Active' status orders. How many rows remain?</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>27</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to keep only orders with Sales_Amount greater than $500. How many high-value orders are there?</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to keep only orders with Quantity greater than 2. How many bulk orders are there?</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to keep orders from January 2024 only (Order_Date between 2024-01-01 and 2024-01-31). How many January orders?</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to keep orders where Discount is greater than 10%. How many high-discount orders?</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>31</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Remove rows where 'Customer_Notes' column is blank or null. How many rows with notes remain?</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Keep only the first 20 rows of the dataset for testing purposes. How many rows remain?</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Keep the last 15 rows of the dataset. How many rows remain?</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Keep a range of rows from row 11 to row 30 (20 rows total). How many rows remain?</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Remove rows where 'Region' is 'North' and 'Category' is 'Electronics' simultaneously. How many rows are removed?</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows where 'Region' is 'North' OR 'Region' is 'West'. How many rows from these regions?</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows where Sales_Amount is between $100 and $500. How many orders in this range?</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to remove orders with negative profit (loss). How many profitable orders remain?</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows where 'Return_Flag' is 'Y'. Create a separate query for returned orders. How many returned orders?</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Remove rows where 'Order_Date' is in the future (after today's date). How many rows are removed?</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Editing Rows</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Filter rows to keep only orders from Q1 2024 (January to March). Then create a new query named 'Q1_2024_Sales'. How many Q1 orders?</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>